--- a/cour/cour_formation/Licence LG02501A_Calculer votre moyenne pondérée 1.xlsx
+++ b/cour/cour_formation/Licence LG02501A_Calculer votre moyenne pondérée 1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\torrs\Documents\GitHub\Dossier-Projet\cour\cour_formation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A6F7EB-D195-4520-B432-3FCC6C2DA2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D6C336-66B3-4FD0-A8AA-3026652164B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Licence" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="69">
   <si>
     <t>UTC501</t>
   </si>
@@ -120,15 +120,6 @@
   </si>
   <si>
     <t>GDN100</t>
-  </si>
-  <si>
-    <t>UE1</t>
-  </si>
-  <si>
-    <t>UE2</t>
-  </si>
-  <si>
-    <t>UE3</t>
   </si>
   <si>
     <t>Coefficient</t>
@@ -1258,7 +1249,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.1796875" customWidth="1"/>
@@ -1270,66 +1261,66 @@
     <col min="7" max="7" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B1" s="34"/>
       <c r="C1" s="3"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" spans="1:7" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="13.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="35" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
       <c r="E3" s="35"/>
     </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="26"/>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
     </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="32" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B5" s="41"/>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
     </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>66</v>
-      </c>
       <c r="E7" s="16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="18" t="s">
         <v>0</v>
       </c>
@@ -1349,7 +1340,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="17" t="s">
         <v>1</v>
       </c>
@@ -1369,7 +1360,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="17" t="s">
         <v>2</v>
       </c>
@@ -1389,7 +1380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="17" t="s">
         <v>3</v>
       </c>
@@ -1409,7 +1400,7 @@
         <v>14.3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="17" t="s">
         <v>4</v>
       </c>
@@ -1428,12 +1419,8 @@
         <f t="shared" si="2"/>
         <v>7.5</v>
       </c>
-      <c r="G12">
-        <f>E18/5</f>
-        <v>34.200000000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="17" t="s">
         <v>5</v>
       </c>
@@ -1446,14 +1433,14 @@
         <v>1</v>
       </c>
       <c r="D13" s="27">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="E13" s="23">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="17" t="s">
         <v>6</v>
       </c>
@@ -1466,16 +1453,16 @@
         <v>1</v>
       </c>
       <c r="D14" s="27">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" s="23">
         <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="20" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B15" s="28">
         <f>IF(VLOOKUP($A15,Tableau_UE,1,TRUE)=$A15,VLOOKUP($A15,Tableau_UE,2,FALSE),6)</f>
@@ -1486,19 +1473,19 @@
         <v>3</v>
       </c>
       <c r="D15" s="27">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="E15" s="29">
         <f t="shared" si="2"/>
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="20" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B16" s="28">
         <f>IF(VLOOKUP($A16,Tableau_UE,1,TRUE)=$A16,VLOOKUP($A16,Tableau_UE,2,FALSE),6)</f>
@@ -1509,17 +1496,17 @@
         <v>3</v>
       </c>
       <c r="D16" s="27">
-        <v>5.5</v>
+        <v>15.4</v>
       </c>
       <c r="E16" s="29">
         <f t="shared" si="2"/>
-        <v>16.5</v>
+        <v>46.2</v>
       </c>
       <c r="F16" s="37"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="21" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B17" s="30">
         <f>IF(VLOOKUP($A17,Tableau_UE,1,TRUE)=$A17,VLOOKUP($A17,Tableau_UE,2,FALSE),6)</f>
@@ -1530,11 +1517,11 @@
         <v>3</v>
       </c>
       <c r="D17" s="27">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="E17" s="31">
         <f t="shared" si="2"/>
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="F17" s="37"/>
     </row>
@@ -1547,7 +1534,7 @@
       </c>
       <c r="E18" s="24">
         <f>SUM(E8:E17)</f>
-        <v>171</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1557,14 +1544,14 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="38" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B20" s="38"/>
       <c r="C20" s="38"/>
       <c r="D20" s="38"/>
       <c r="E20" s="25">
         <f>E18/C18</f>
-        <v>10.6875</v>
+        <v>12.25</v>
       </c>
     </row>
   </sheetData>
@@ -1604,13 +1591,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -1626,7 +1613,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B3" s="6">
         <v>6</v>
@@ -1637,7 +1624,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B4" s="6">
         <v>6</v>
@@ -1648,7 +1635,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="6">
         <v>6</v>
@@ -1657,12 +1644,12 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B6" s="6">
         <v>6</v>
@@ -1684,7 +1671,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6">
         <v>6</v>
@@ -1695,7 +1682,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9" s="8">
         <v>6</v>
@@ -1706,7 +1693,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B10" s="6">
         <v>6</v>
@@ -1717,7 +1704,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B11" s="6">
         <v>6</v>
@@ -1728,7 +1715,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B12" s="6">
         <v>4</v>
@@ -1739,7 +1726,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B13" s="6">
         <v>4</v>
@@ -1750,7 +1737,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B14" s="6">
         <v>4</v>
@@ -1761,7 +1748,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B15" s="6">
         <v>4</v>
@@ -1772,7 +1759,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B16" s="6">
         <v>4</v>
@@ -1783,7 +1770,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B17" s="6">
         <v>6</v>
@@ -1794,7 +1781,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B18" s="6">
         <v>6</v>
@@ -1805,7 +1792,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6">
         <v>6</v>
@@ -1816,7 +1803,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B20" s="6">
         <v>4</v>
@@ -1827,7 +1814,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B21" s="6">
         <v>4</v>
@@ -1838,7 +1825,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B22" s="6">
         <v>4</v>
@@ -1849,7 +1836,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B23" s="6">
         <v>4</v>
@@ -1860,7 +1847,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B24" s="6">
         <v>4</v>
@@ -1871,7 +1858,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B25" s="6">
         <v>6</v>
@@ -1882,7 +1869,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B26" s="6">
         <v>6</v>
@@ -1893,7 +1880,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B27" s="6">
         <v>4</v>
@@ -1904,7 +1891,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B28" s="6">
         <v>6</v>
@@ -1915,7 +1902,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B29" s="6">
         <v>6</v>
@@ -1926,7 +1913,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B30" s="6">
         <v>6</v>
@@ -1937,7 +1924,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B31" s="6">
         <v>6</v>
@@ -1948,7 +1935,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B32" s="6">
         <v>4</v>
@@ -1959,7 +1946,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B33" s="6">
         <v>6</v>
@@ -1970,7 +1957,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B34" s="6">
         <v>6</v>
@@ -1981,7 +1968,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B35" s="6">
         <v>6</v>
@@ -1992,7 +1979,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B36" s="6">
         <v>6</v>
@@ -2003,7 +1990,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B37" s="6">
         <v>6</v>
@@ -2014,7 +2001,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B38" s="6">
         <v>6</v>
@@ -2025,7 +2012,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B39" s="6">
         <v>6</v>
@@ -2036,7 +2023,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B40" s="6">
         <v>6</v>
@@ -2047,7 +2034,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B41" s="6">
         <v>6</v>
@@ -2058,7 +2045,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B42" s="6">
         <v>6</v>
@@ -2069,7 +2056,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B43" s="6">
         <v>6</v>
@@ -2080,7 +2067,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B44" s="6">
         <v>6</v>
@@ -2091,7 +2078,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B45" s="6">
         <v>6</v>
@@ -2102,7 +2089,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B46" s="6">
         <v>6</v>
@@ -2113,7 +2100,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B47" s="6">
         <v>6</v>
@@ -2122,12 +2109,12 @@
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B48" s="6">
         <v>6</v>
@@ -2136,12 +2123,12 @@
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B49" s="6">
         <v>6</v>
@@ -2152,7 +2139,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B50" s="8">
         <v>6</v>
@@ -2163,7 +2150,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B51" s="8">
         <v>6</v>
@@ -2172,12 +2159,12 @@
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B52" s="6">
         <v>6</v>
